--- a/bases/RODA_alunos.xlsx
+++ b/bases/RODA_alunos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Angelus\Dropbox\prouenf\arquivos de análise\T6 - Aplicativo Coordenação\Sistema_V1\Bases\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemas\Dropbox\prouenf\arquivos de análise\T6 - Aplicativo Coordenação\Sistema_V1\streamlit_local\bases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12194879-061C-45A0-AF1E-880EDB4BE348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2125F691-397B-42C6-9BD0-FD50EA1766B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="252">
   <si>
     <t>matrícula</t>
   </si>
@@ -41,12 +41,6 @@
   </si>
   <si>
     <t>EPL</t>
-  </si>
-  <si>
-    <t>Reativação Matrícula</t>
-  </si>
-  <si>
-    <t>Condição Especial</t>
   </si>
   <si>
     <t>20261100032</t>
@@ -1145,17 +1139,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I106"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="44.5703125" customWidth="1"/>
-    <col min="4" max="4" width="28.5703125" customWidth="1"/>
-    <col min="5" max="5" width="24.42578125" customWidth="1"/>
-    <col min="8" max="8" width="20.85546875" customWidth="1"/>
-    <col min="9" max="9" width="22.85546875" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" customWidth="1"/>
+    <col min="2" max="2" width="44.5546875" customWidth="1"/>
+    <col min="4" max="4" width="28.5546875" customWidth="1"/>
+    <col min="5" max="5" width="24.44140625" customWidth="1"/>
+    <col min="8" max="8" width="20.88671875" customWidth="1"/>
+    <col min="9" max="9" width="22.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1177,2177 +1171,1555 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="B2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
         <v>11</v>
       </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="H2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="C3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
       </c>
       <c r="F3">
         <v>0.28999999999999998</v>
       </c>
-      <c r="H3" t="b">
-        <v>0</v>
-      </c>
-      <c r="I3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>0.45</v>
       </c>
-      <c r="H4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
         <v>19</v>
-      </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" t="s">
-        <v>21</v>
       </c>
       <c r="G5">
         <v>0.61</v>
       </c>
-      <c r="H5" t="b">
-        <v>0</v>
-      </c>
-      <c r="I5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G6">
         <v>0.44</v>
       </c>
-      <c r="H6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" t="s">
         <v>24</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" t="s">
-        <v>26</v>
       </c>
       <c r="G7">
         <v>0.5</v>
       </c>
-      <c r="H7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>27</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B9" t="s">
         <v>28</v>
       </c>
-      <c r="C8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="H8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="C9" t="s">
         <v>29</v>
-      </c>
-      <c r="B9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" t="s">
-        <v>31</v>
       </c>
       <c r="G9">
         <v>0.66</v>
       </c>
-      <c r="H9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" t="s">
         <v>32</v>
-      </c>
-      <c r="B10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" t="s">
-        <v>34</v>
       </c>
       <c r="G10">
         <v>0.36</v>
       </c>
-      <c r="H10" t="b">
-        <v>0</v>
-      </c>
-      <c r="I10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>35</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B12" t="s">
         <v>36</v>
       </c>
-      <c r="C11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="H11" t="b">
-        <v>0</v>
-      </c>
-      <c r="I11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="C12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>37</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B13" t="s">
         <v>38</v>
       </c>
-      <c r="C12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="H12" t="b">
-        <v>0</v>
-      </c>
-      <c r="I12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="C13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>39</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B14" t="s">
         <v>40</v>
       </c>
-      <c r="C13" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="H13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>41</v>
-      </c>
-      <c r="B14" t="s">
-        <v>42</v>
-      </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G14">
         <v>0.41</v>
       </c>
-      <c r="H14" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" t="s">
         <v>43</v>
       </c>
-      <c r="B15" t="s">
+      <c r="D15" t="s">
         <v>44</v>
       </c>
-      <c r="C15" t="s">
+      <c r="E15" t="s">
         <v>45</v>
-      </c>
-      <c r="D15" t="s">
-        <v>46</v>
-      </c>
-      <c r="E15" t="s">
-        <v>47</v>
       </c>
       <c r="G15">
         <v>0.45</v>
       </c>
-      <c r="H15" t="b">
-        <v>0</v>
-      </c>
-      <c r="I15" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C16" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G16">
         <v>0.59</v>
       </c>
-      <c r="H16" t="b">
-        <v>0</v>
-      </c>
-      <c r="I16" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C17" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G17">
         <v>0.44</v>
       </c>
-      <c r="H17" t="b">
-        <v>0</v>
-      </c>
-      <c r="I17" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" t="s">
         <v>52</v>
-      </c>
-      <c r="B18" t="s">
-        <v>53</v>
-      </c>
-      <c r="C18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D18" t="s">
-        <v>54</v>
       </c>
       <c r="G18">
         <v>0.37</v>
       </c>
-      <c r="H18" t="b">
-        <v>0</v>
-      </c>
-      <c r="I18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>55</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B20" t="s">
         <v>56</v>
       </c>
-      <c r="C19" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="H19" t="b">
-        <v>0</v>
-      </c>
-      <c r="I19" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>57</v>
-      </c>
-      <c r="B20" t="s">
-        <v>58</v>
-      </c>
       <c r="C20" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G20">
         <v>0.68</v>
       </c>
-      <c r="H20" t="b">
-        <v>0</v>
-      </c>
-      <c r="I20" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>59</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B22" t="s">
         <v>60</v>
       </c>
-      <c r="C21" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="H21" t="b">
-        <v>0</v>
-      </c>
-      <c r="I21" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>61</v>
-      </c>
-      <c r="B22" t="s">
-        <v>62</v>
-      </c>
       <c r="C22" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G22">
         <v>0.69</v>
       </c>
-      <c r="H22" t="b">
-        <v>0</v>
-      </c>
-      <c r="I22" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>61</v>
+      </c>
+      <c r="B23" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>63</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B24" t="s">
         <v>64</v>
       </c>
-      <c r="C23" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23">
-        <v>0</v>
-      </c>
-      <c r="H23" t="b">
-        <v>0</v>
-      </c>
-      <c r="I23" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="C24" t="s">
         <v>65</v>
       </c>
-      <c r="B24" t="s">
+      <c r="D24" t="s">
         <v>66</v>
       </c>
-      <c r="C24" t="s">
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>67</v>
       </c>
-      <c r="D24" t="s">
+      <c r="B25" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="C25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>69</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B26" t="s">
         <v>70</v>
       </c>
-      <c r="C25" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25">
-        <v>0</v>
-      </c>
-      <c r="H25" t="b">
-        <v>0</v>
-      </c>
-      <c r="I25" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="C26" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>71</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B27" t="s">
         <v>72</v>
       </c>
-      <c r="C26" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26">
-        <v>0</v>
-      </c>
-      <c r="H26" t="b">
-        <v>0</v>
-      </c>
-      <c r="I26" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>73</v>
-      </c>
-      <c r="B27" t="s">
-        <v>74</v>
-      </c>
       <c r="C27" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G27">
         <v>0.39</v>
       </c>
-      <c r="H27" t="b">
-        <v>0</v>
-      </c>
-      <c r="I27" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B28" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C28" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G28">
         <v>0.64</v>
       </c>
-      <c r="H28" t="b">
-        <v>0</v>
-      </c>
-      <c r="I28" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>75</v>
+      </c>
+      <c r="B29" t="s">
+        <v>76</v>
+      </c>
+      <c r="C29" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>77</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B30" t="s">
         <v>78</v>
       </c>
-      <c r="C29" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29">
-        <v>0</v>
-      </c>
-      <c r="H29" t="b">
-        <v>0</v>
-      </c>
-      <c r="I29" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="C30" t="s">
+        <v>9</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>79</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B31" t="s">
         <v>80</v>
       </c>
-      <c r="C30" t="s">
-        <v>11</v>
-      </c>
-      <c r="F30">
-        <v>0</v>
-      </c>
-      <c r="H30" t="b">
-        <v>0</v>
-      </c>
-      <c r="I30" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>81</v>
-      </c>
-      <c r="B31" t="s">
-        <v>82</v>
-      </c>
       <c r="C31" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G31">
         <v>0.52</v>
       </c>
-      <c r="H31" t="b">
-        <v>0</v>
-      </c>
-      <c r="I31" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>81</v>
+      </c>
+      <c r="B32" t="s">
+        <v>82</v>
+      </c>
+      <c r="C32" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>83</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B33" t="s">
         <v>84</v>
       </c>
-      <c r="C32" t="s">
-        <v>11</v>
-      </c>
-      <c r="F32">
-        <v>0</v>
-      </c>
-      <c r="H32" t="b">
-        <v>0</v>
-      </c>
-      <c r="I32" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>85</v>
-      </c>
-      <c r="B33" t="s">
-        <v>86</v>
-      </c>
       <c r="C33" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G33">
         <v>0.45</v>
       </c>
-      <c r="H33" t="b">
-        <v>0</v>
-      </c>
-      <c r="I33" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>85</v>
+      </c>
+      <c r="B34" t="s">
+        <v>86</v>
+      </c>
+      <c r="C34" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
         <v>87</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B35" t="s">
         <v>88</v>
       </c>
-      <c r="C34" t="s">
-        <v>11</v>
-      </c>
-      <c r="F34">
-        <v>0</v>
-      </c>
-      <c r="H34" t="b">
-        <v>0</v>
-      </c>
-      <c r="I34" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>89</v>
-      </c>
-      <c r="B35" t="s">
-        <v>90</v>
-      </c>
       <c r="C35" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G35">
         <v>0.67</v>
       </c>
-      <c r="H35" t="b">
-        <v>0</v>
-      </c>
-      <c r="I35" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>89</v>
+      </c>
+      <c r="B36" t="s">
+        <v>90</v>
+      </c>
+      <c r="C36" t="s">
+        <v>29</v>
+      </c>
+      <c r="E36" t="s">
         <v>91</v>
-      </c>
-      <c r="B36" t="s">
-        <v>92</v>
-      </c>
-      <c r="C36" t="s">
-        <v>31</v>
-      </c>
-      <c r="E36" t="s">
-        <v>93</v>
       </c>
       <c r="G36">
         <v>0.2</v>
       </c>
-      <c r="H36" t="b">
-        <v>0</v>
-      </c>
-      <c r="I36" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>92</v>
+      </c>
+      <c r="B37" t="s">
+        <v>93</v>
+      </c>
+      <c r="C37" t="s">
+        <v>32</v>
+      </c>
+      <c r="E37" t="s">
         <v>94</v>
-      </c>
-      <c r="B37" t="s">
-        <v>95</v>
-      </c>
-      <c r="C37" t="s">
-        <v>34</v>
-      </c>
-      <c r="E37" t="s">
-        <v>96</v>
       </c>
       <c r="G37">
         <v>0.27</v>
       </c>
-      <c r="H37" t="b">
-        <v>0</v>
-      </c>
-      <c r="I37" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B38" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C38" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G38">
         <v>0.49</v>
       </c>
-      <c r="H38" t="b">
-        <v>0</v>
-      </c>
-      <c r="I38" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>97</v>
+      </c>
+      <c r="B39" t="s">
+        <v>98</v>
+      </c>
+      <c r="C39" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>99</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B40" t="s">
         <v>100</v>
       </c>
-      <c r="C39" t="s">
-        <v>11</v>
-      </c>
-      <c r="F39">
-        <v>0</v>
-      </c>
-      <c r="H39" t="b">
-        <v>0</v>
-      </c>
-      <c r="I39" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+      <c r="C40" t="s">
+        <v>9</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>101</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B41" t="s">
         <v>102</v>
       </c>
-      <c r="C40" t="s">
-        <v>11</v>
-      </c>
-      <c r="F40">
-        <v>0</v>
-      </c>
-      <c r="H40" t="b">
-        <v>0</v>
-      </c>
-      <c r="I40" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>103</v>
-      </c>
-      <c r="B41" t="s">
-        <v>104</v>
-      </c>
       <c r="C41" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G41">
         <v>0.47</v>
       </c>
-      <c r="H41" t="b">
-        <v>0</v>
-      </c>
-      <c r="I41" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>103</v>
+      </c>
+      <c r="B42" t="s">
+        <v>104</v>
+      </c>
+      <c r="C42" t="s">
+        <v>9</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>105</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B43" t="s">
         <v>106</v>
       </c>
-      <c r="C42" t="s">
-        <v>11</v>
-      </c>
-      <c r="F42">
-        <v>0</v>
-      </c>
-      <c r="H42" t="b">
-        <v>0</v>
-      </c>
-      <c r="I42" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+      <c r="C43" t="s">
         <v>107</v>
-      </c>
-      <c r="B43" t="s">
-        <v>108</v>
-      </c>
-      <c r="C43" t="s">
-        <v>109</v>
       </c>
       <c r="G43">
         <v>0.37</v>
       </c>
-      <c r="H43" t="b">
-        <v>0</v>
-      </c>
-      <c r="I43" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>108</v>
+      </c>
+      <c r="B44" t="s">
+        <v>109</v>
+      </c>
+      <c r="C44" t="s">
+        <v>12</v>
+      </c>
+      <c r="D44" t="s">
         <v>110</v>
-      </c>
-      <c r="B44" t="s">
-        <v>111</v>
-      </c>
-      <c r="C44" t="s">
-        <v>14</v>
-      </c>
-      <c r="D44" t="s">
-        <v>112</v>
       </c>
       <c r="G44">
         <v>0.5</v>
       </c>
-      <c r="H44" t="b">
-        <v>0</v>
-      </c>
-      <c r="I44" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
+        <v>111</v>
+      </c>
+      <c r="B45" t="s">
+        <v>112</v>
+      </c>
+      <c r="C45" t="s">
+        <v>9</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
         <v>113</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B46" t="s">
         <v>114</v>
       </c>
-      <c r="C45" t="s">
-        <v>11</v>
-      </c>
-      <c r="F45">
-        <v>0</v>
-      </c>
-      <c r="H45" t="b">
-        <v>0</v>
-      </c>
-      <c r="I45" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+      <c r="C46" t="s">
+        <v>32</v>
+      </c>
+      <c r="D46" t="s">
         <v>115</v>
       </c>
-      <c r="B46" t="s">
+      <c r="E46" t="s">
         <v>116</v>
-      </c>
-      <c r="C46" t="s">
-        <v>34</v>
-      </c>
-      <c r="D46" t="s">
-        <v>117</v>
-      </c>
-      <c r="E46" t="s">
-        <v>118</v>
       </c>
       <c r="G46">
         <v>0.26</v>
       </c>
-      <c r="H46" t="b">
-        <v>0</v>
-      </c>
-      <c r="I46" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
+        <v>117</v>
+      </c>
+      <c r="B47" t="s">
+        <v>118</v>
+      </c>
+      <c r="C47" t="s">
+        <v>9</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
         <v>119</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B48" t="s">
         <v>120</v>
       </c>
-      <c r="C47" t="s">
-        <v>11</v>
-      </c>
-      <c r="F47">
-        <v>0</v>
-      </c>
-      <c r="H47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I47" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+      <c r="C48" t="s">
         <v>121</v>
       </c>
-      <c r="B48" t="s">
+      <c r="D48" t="s">
         <v>122</v>
       </c>
-      <c r="C48" t="s">
+      <c r="E48" t="s">
         <v>123</v>
-      </c>
-      <c r="D48" t="s">
-        <v>124</v>
-      </c>
-      <c r="E48" t="s">
-        <v>125</v>
       </c>
       <c r="G48">
         <v>0.31</v>
       </c>
-      <c r="H48" t="b">
-        <v>0</v>
-      </c>
-      <c r="I48" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B49" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C49" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G49">
         <v>0.63</v>
       </c>
-      <c r="H49" t="b">
-        <v>0</v>
-      </c>
-      <c r="I49" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B50" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C50" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G50">
         <v>0.46</v>
       </c>
-      <c r="H50" t="b">
-        <v>0</v>
-      </c>
-      <c r="I50" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B51" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C51" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G51">
         <v>0.69</v>
       </c>
-      <c r="H51" t="b">
-        <v>0</v>
-      </c>
-      <c r="I51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
+        <v>130</v>
+      </c>
+      <c r="B52" t="s">
+        <v>131</v>
+      </c>
+      <c r="C52" t="s">
+        <v>12</v>
+      </c>
+      <c r="D52" t="s">
         <v>132</v>
       </c>
-      <c r="B52" t="s">
+      <c r="E52" t="s">
         <v>133</v>
-      </c>
-      <c r="C52" t="s">
-        <v>14</v>
-      </c>
-      <c r="D52" t="s">
-        <v>134</v>
-      </c>
-      <c r="E52" t="s">
-        <v>135</v>
       </c>
       <c r="F52">
         <v>0.44</v>
       </c>
-      <c r="H52" t="b">
-        <v>0</v>
-      </c>
-      <c r="I52" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B53" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C53" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G53">
         <v>0.56999999999999995</v>
       </c>
-      <c r="H53" t="b">
-        <v>0</v>
-      </c>
-      <c r="I53" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B54" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C54" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G54">
         <v>0.45</v>
       </c>
-      <c r="H54" t="b">
-        <v>0</v>
-      </c>
-      <c r="I54" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B55" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C55" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G55">
         <v>0.59</v>
       </c>
-      <c r="H55" t="b">
-        <v>0</v>
-      </c>
-      <c r="I55" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B56" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C56" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G56">
         <v>0.6</v>
       </c>
-      <c r="H56" t="b">
-        <v>0</v>
-      </c>
-      <c r="I56" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
+        <v>142</v>
+      </c>
+      <c r="B57" t="s">
+        <v>143</v>
+      </c>
+      <c r="C57" t="s">
+        <v>9</v>
+      </c>
+      <c r="F57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
         <v>144</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B58" t="s">
         <v>145</v>
       </c>
-      <c r="C57" t="s">
-        <v>11</v>
-      </c>
-      <c r="F57">
-        <v>0</v>
-      </c>
-      <c r="H57" t="b">
-        <v>0</v>
-      </c>
-      <c r="I57" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+      <c r="C58" t="s">
+        <v>9</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
         <v>146</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B59" t="s">
         <v>147</v>
       </c>
-      <c r="C58" t="s">
-        <v>11</v>
-      </c>
-      <c r="F58">
-        <v>0</v>
-      </c>
-      <c r="H58" t="b">
-        <v>0</v>
-      </c>
-      <c r="I58" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>148</v>
-      </c>
-      <c r="B59" t="s">
-        <v>149</v>
-      </c>
       <c r="C59" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G59">
         <v>0.61</v>
       </c>
-      <c r="H59" t="b">
-        <v>0</v>
-      </c>
-      <c r="I59" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B60" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C60" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G60">
         <v>0.68</v>
       </c>
-      <c r="H60" t="b">
-        <v>0</v>
-      </c>
-      <c r="I60" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
+        <v>150</v>
+      </c>
+      <c r="B61" t="s">
+        <v>151</v>
+      </c>
+      <c r="C61" t="s">
+        <v>9</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
         <v>152</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B62" t="s">
         <v>153</v>
       </c>
-      <c r="C61" t="s">
-        <v>11</v>
-      </c>
-      <c r="F61">
-        <v>0</v>
-      </c>
-      <c r="H61" t="b">
-        <v>0</v>
-      </c>
-      <c r="I61" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>154</v>
-      </c>
-      <c r="B62" t="s">
-        <v>155</v>
-      </c>
       <c r="C62" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G62">
         <v>0.45</v>
       </c>
-      <c r="H62" t="b">
-        <v>0</v>
-      </c>
-      <c r="I62" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B63" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C63" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G63">
         <v>0.45</v>
       </c>
-      <c r="H63" t="b">
-        <v>0</v>
-      </c>
-      <c r="I63" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
+        <v>156</v>
+      </c>
+      <c r="B64" t="s">
+        <v>157</v>
+      </c>
+      <c r="C64" t="s">
+        <v>65</v>
+      </c>
+      <c r="D64" t="s">
         <v>158</v>
-      </c>
-      <c r="B64" t="s">
-        <v>159</v>
-      </c>
-      <c r="C64" t="s">
-        <v>67</v>
-      </c>
-      <c r="D64" t="s">
-        <v>160</v>
       </c>
       <c r="G64">
         <v>0.63</v>
       </c>
-      <c r="H64" t="b">
-        <v>0</v>
-      </c>
-      <c r="I64" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B65" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C65" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G65">
         <v>0.69</v>
       </c>
-      <c r="H65" t="b">
-        <v>0</v>
-      </c>
-      <c r="I65" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B66" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C66" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G66">
         <v>0.46</v>
       </c>
-      <c r="H66" t="b">
-        <v>0</v>
-      </c>
-      <c r="I66" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B67" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C67" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G67">
         <v>0.6</v>
       </c>
-      <c r="H67" t="b">
-        <v>0</v>
-      </c>
-      <c r="I67" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B68" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C68" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E68" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G68">
         <v>0.27</v>
       </c>
-      <c r="H68" t="b">
-        <v>0</v>
-      </c>
-      <c r="I68" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
+        <v>167</v>
+      </c>
+      <c r="B69" t="s">
+        <v>168</v>
+      </c>
+      <c r="C69" t="s">
+        <v>121</v>
+      </c>
+      <c r="D69" t="s">
         <v>169</v>
       </c>
-      <c r="B69" t="s">
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
         <v>170</v>
       </c>
-      <c r="C69" t="s">
-        <v>123</v>
-      </c>
-      <c r="D69" t="s">
+      <c r="B70" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>172</v>
-      </c>
-      <c r="B70" t="s">
-        <v>173</v>
-      </c>
       <c r="C70" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G70">
         <v>0.64</v>
       </c>
-      <c r="H70" t="b">
-        <v>0</v>
-      </c>
-      <c r="I70" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
+        <v>172</v>
+      </c>
+      <c r="B71" t="s">
+        <v>173</v>
+      </c>
+      <c r="C71" t="s">
+        <v>12</v>
+      </c>
+      <c r="E71" t="s">
         <v>174</v>
-      </c>
-      <c r="B71" t="s">
-        <v>175</v>
-      </c>
-      <c r="C71" t="s">
-        <v>14</v>
-      </c>
-      <c r="E71" t="s">
-        <v>176</v>
       </c>
       <c r="G71">
         <v>0.38</v>
       </c>
-      <c r="H71" t="b">
-        <v>0</v>
-      </c>
-      <c r="I71" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B72" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C72" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G72">
         <v>0.45</v>
       </c>
-      <c r="H72" t="b">
-        <v>0</v>
-      </c>
-      <c r="I72" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>177</v>
+      </c>
+      <c r="B73" t="s">
+        <v>178</v>
+      </c>
+      <c r="C73" t="s">
+        <v>9</v>
+      </c>
+      <c r="F73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
         <v>179</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B74" t="s">
         <v>180</v>
       </c>
-      <c r="C73" t="s">
-        <v>11</v>
-      </c>
-      <c r="F73">
-        <v>0</v>
-      </c>
-      <c r="H73" t="b">
-        <v>0</v>
-      </c>
-      <c r="I73" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>181</v>
-      </c>
-      <c r="B74" t="s">
-        <v>182</v>
-      </c>
       <c r="C74" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G74">
         <v>0.49</v>
       </c>
-      <c r="H74" t="b">
-        <v>0</v>
-      </c>
-      <c r="I74" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B75" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C75" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E75" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G75">
         <v>0.41</v>
       </c>
-      <c r="H75" t="b">
-        <v>0</v>
-      </c>
-      <c r="I75" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
+        <v>183</v>
+      </c>
+      <c r="B76" t="s">
+        <v>184</v>
+      </c>
+      <c r="C76" t="s">
+        <v>121</v>
+      </c>
+      <c r="D76" t="s">
         <v>185</v>
       </c>
-      <c r="B76" t="s">
+      <c r="E76" t="s">
         <v>186</v>
-      </c>
-      <c r="C76" t="s">
-        <v>123</v>
-      </c>
-      <c r="D76" t="s">
-        <v>187</v>
-      </c>
-      <c r="E76" t="s">
-        <v>188</v>
       </c>
       <c r="F76">
         <v>0.37</v>
       </c>
-      <c r="H76" t="b">
-        <v>0</v>
-      </c>
-      <c r="I76" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B77" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C77" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G77">
         <v>0.54</v>
       </c>
-      <c r="H77" t="b">
-        <v>0</v>
-      </c>
-      <c r="I77" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B78" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C78" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G78">
         <v>0.67</v>
       </c>
-      <c r="H78" t="b">
-        <v>0</v>
-      </c>
-      <c r="I78" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
+        <v>191</v>
+      </c>
+      <c r="B79" t="s">
+        <v>192</v>
+      </c>
+      <c r="C79" t="s">
+        <v>9</v>
+      </c>
+      <c r="F79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
         <v>193</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B80" t="s">
         <v>194</v>
       </c>
-      <c r="C79" t="s">
-        <v>11</v>
-      </c>
-      <c r="F79">
-        <v>0</v>
-      </c>
-      <c r="H79" t="b">
-        <v>0</v>
-      </c>
-      <c r="I79" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>195</v>
-      </c>
-      <c r="B80" t="s">
-        <v>196</v>
-      </c>
       <c r="C80" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G80">
         <v>0.56000000000000005</v>
       </c>
-      <c r="H80" t="b">
-        <v>0</v>
-      </c>
-      <c r="I80" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
+        <v>195</v>
+      </c>
+      <c r="B81" t="s">
+        <v>196</v>
+      </c>
+      <c r="C81" t="s">
+        <v>9</v>
+      </c>
+      <c r="F81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
         <v>197</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B82" t="s">
         <v>198</v>
       </c>
-      <c r="C81" t="s">
-        <v>11</v>
-      </c>
-      <c r="F81">
-        <v>0</v>
-      </c>
-      <c r="H81" t="b">
-        <v>0</v>
-      </c>
-      <c r="I81" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>199</v>
-      </c>
-      <c r="B82" t="s">
-        <v>200</v>
-      </c>
       <c r="C82" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G82">
         <v>0.49</v>
       </c>
-      <c r="H82" t="b">
-        <v>0</v>
-      </c>
-      <c r="I82" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B83" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C83" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G83">
         <v>0.51</v>
       </c>
-      <c r="H83" t="b">
-        <v>0</v>
-      </c>
-      <c r="I83" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B84" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C84" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G84">
         <v>0.45</v>
       </c>
-      <c r="H84" t="b">
-        <v>0</v>
-      </c>
-      <c r="I84" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
+        <v>203</v>
+      </c>
+      <c r="B85" t="s">
+        <v>204</v>
+      </c>
+      <c r="C85" t="s">
         <v>205</v>
-      </c>
-      <c r="B85" t="s">
-        <v>206</v>
-      </c>
-      <c r="C85" t="s">
-        <v>207</v>
       </c>
       <c r="G85">
         <v>0.34</v>
       </c>
-      <c r="H85" t="b">
-        <v>0</v>
-      </c>
-      <c r="I85" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
+        <v>206</v>
+      </c>
+      <c r="B86" t="s">
+        <v>207</v>
+      </c>
+      <c r="C86" t="s">
+        <v>9</v>
+      </c>
+      <c r="F86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
         <v>208</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B87" t="s">
         <v>209</v>
       </c>
-      <c r="C86" t="s">
-        <v>11</v>
-      </c>
-      <c r="F86">
-        <v>0</v>
-      </c>
-      <c r="H86" t="b">
-        <v>0</v>
-      </c>
-      <c r="I86" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
+      <c r="C87" t="s">
+        <v>12</v>
+      </c>
+      <c r="D87" t="s">
         <v>210</v>
       </c>
-      <c r="B87" t="s">
-        <v>211</v>
-      </c>
-      <c r="C87" t="s">
-        <v>14</v>
-      </c>
-      <c r="D87" t="s">
-        <v>212</v>
-      </c>
       <c r="E87" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F87">
         <v>0.37</v>
       </c>
-      <c r="H87" t="b">
-        <v>0</v>
-      </c>
-      <c r="I87" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
+        <v>211</v>
+      </c>
+      <c r="B88" t="s">
+        <v>212</v>
+      </c>
+      <c r="C88" t="s">
+        <v>9</v>
+      </c>
+      <c r="F88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
         <v>213</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B89" t="s">
         <v>214</v>
       </c>
-      <c r="C88" t="s">
-        <v>11</v>
-      </c>
-      <c r="F88">
-        <v>0</v>
-      </c>
-      <c r="H88" t="b">
-        <v>0</v>
-      </c>
-      <c r="I88" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>215</v>
-      </c>
-      <c r="B89" t="s">
-        <v>216</v>
-      </c>
       <c r="C89" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G89">
         <v>0.65</v>
       </c>
-      <c r="H89" t="b">
-        <v>0</v>
-      </c>
-      <c r="I89" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
+        <v>215</v>
+      </c>
+      <c r="B90" t="s">
+        <v>216</v>
+      </c>
+      <c r="C90" t="s">
+        <v>9</v>
+      </c>
+      <c r="F90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
         <v>217</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B91" t="s">
         <v>218</v>
       </c>
-      <c r="C90" t="s">
-        <v>11</v>
-      </c>
-      <c r="F90">
-        <v>0</v>
-      </c>
-      <c r="H90" t="b">
-        <v>0</v>
-      </c>
-      <c r="I90" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>219</v>
-      </c>
-      <c r="B91" t="s">
-        <v>220</v>
-      </c>
       <c r="C91" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G91">
         <v>0.56999999999999995</v>
       </c>
-      <c r="H91" t="b">
-        <v>0</v>
-      </c>
-      <c r="I91" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B92" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C92" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G92">
         <v>0.49</v>
       </c>
-      <c r="H92" t="b">
-        <v>0</v>
-      </c>
-      <c r="I92" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B93" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C93" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G93">
         <v>0.56000000000000005</v>
       </c>
-      <c r="H93" t="b">
-        <v>0</v>
-      </c>
-      <c r="I93" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B94" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C94" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G94">
         <v>0.39</v>
       </c>
-      <c r="H94" t="b">
-        <v>0</v>
-      </c>
-      <c r="I94" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
+        <v>225</v>
+      </c>
+      <c r="B95" t="s">
+        <v>226</v>
+      </c>
+      <c r="C95" t="s">
+        <v>9</v>
+      </c>
+      <c r="F95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
         <v>227</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B96" t="s">
         <v>228</v>
       </c>
-      <c r="C95" t="s">
-        <v>11</v>
-      </c>
-      <c r="F95">
-        <v>0</v>
-      </c>
-      <c r="H95" t="b">
-        <v>0</v>
-      </c>
-      <c r="I95" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
+      <c r="C96" t="s">
+        <v>9</v>
+      </c>
+      <c r="F96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
         <v>229</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B97" t="s">
         <v>230</v>
       </c>
-      <c r="C96" t="s">
-        <v>11</v>
-      </c>
-      <c r="F96">
-        <v>0</v>
-      </c>
-      <c r="H96" t="b">
-        <v>0</v>
-      </c>
-      <c r="I96" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>231</v>
-      </c>
-      <c r="B97" t="s">
-        <v>232</v>
-      </c>
       <c r="C97" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G97">
         <v>0.54</v>
       </c>
-      <c r="H97" t="b">
-        <v>0</v>
-      </c>
-      <c r="I97" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B98" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C98" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G98">
         <v>0.62</v>
       </c>
-      <c r="H98" t="b">
-        <v>0</v>
-      </c>
-      <c r="I98" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
+        <v>233</v>
+      </c>
+      <c r="B99" t="s">
+        <v>234</v>
+      </c>
+      <c r="C99" t="s">
+        <v>32</v>
+      </c>
+      <c r="D99" t="s">
         <v>235</v>
-      </c>
-      <c r="B99" t="s">
-        <v>236</v>
-      </c>
-      <c r="C99" t="s">
-        <v>34</v>
-      </c>
-      <c r="D99" t="s">
-        <v>237</v>
       </c>
       <c r="G99">
         <v>0.4</v>
       </c>
-      <c r="H99" t="b">
-        <v>0</v>
-      </c>
-      <c r="I99" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
+        <v>236</v>
+      </c>
+      <c r="B100" t="s">
+        <v>237</v>
+      </c>
+      <c r="C100" t="s">
+        <v>121</v>
+      </c>
+      <c r="E100" t="s">
         <v>238</v>
-      </c>
-      <c r="B100" t="s">
-        <v>239</v>
-      </c>
-      <c r="C100" t="s">
-        <v>123</v>
-      </c>
-      <c r="E100" t="s">
-        <v>240</v>
       </c>
       <c r="G100">
         <v>0.27</v>
       </c>
-      <c r="H100" t="b">
-        <v>0</v>
-      </c>
-      <c r="I100" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B101" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C101" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G101">
         <v>0.68</v>
       </c>
-      <c r="H101" t="b">
-        <v>0</v>
-      </c>
-      <c r="I101" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B102" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C102" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G102">
         <v>0.36</v>
       </c>
-      <c r="H102" t="b">
-        <v>0</v>
-      </c>
-      <c r="I102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B103" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C103" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G103">
         <v>0.45</v>
       </c>
-      <c r="H103" t="b">
-        <v>0</v>
-      </c>
-      <c r="I103" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B104" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C104" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G104">
         <v>0.56000000000000005</v>
       </c>
-      <c r="H104" t="b">
-        <v>0</v>
-      </c>
-      <c r="I104" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
+        <v>247</v>
+      </c>
+      <c r="B105" t="s">
+        <v>248</v>
+      </c>
+      <c r="C105" t="s">
+        <v>32</v>
+      </c>
+      <c r="D105" t="s">
         <v>249</v>
-      </c>
-      <c r="B105" t="s">
-        <v>250</v>
-      </c>
-      <c r="C105" t="s">
-        <v>34</v>
-      </c>
-      <c r="D105" t="s">
-        <v>251</v>
       </c>
       <c r="G105">
         <v>0.3</v>
       </c>
-      <c r="H105" t="b">
-        <v>0</v>
-      </c>
-      <c r="I105" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B106" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C106" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G106">
         <v>0.59</v>
-      </c>
-      <c r="H106" t="b">
-        <v>0</v>
-      </c>
-      <c r="I106" t="b">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
